--- a/test-data/RD_Jachymov_dum/outputs/VYMERY_SOUHRN_2026-06-01.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/VYMERY_SOUHRN_2026-06-01.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VYMERY" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VYMERY'!$A$2:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VYMERY'!$A$2:$I$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -576,12 +576,12 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>S04/S06</t>
+          <t>podlaha S04 · stěna S03 · strop S06</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>půdorys 1.PP stav</t>
+          <t>tabulka místností 1.PP stav</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>0.03 sklep 1</t>
+          <t>0.02 chodba</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>22.2</v>
+        <v>4.4</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -621,12 +621,12 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>S04</t>
+          <t>podlaha S04 · stěna S03 · strop S06</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>půdorys 1.PP stav</t>
+          <t>tabulka místností 1.PP stav</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -638,16 +638,16 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>1.01 vstup+chodba</t>
+          <t>0.03 sklep 1</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>dům 1.NP návrh</t>
+          <t>dům 1.PP</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.1</v>
+        <v>22.2</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -666,12 +666,12 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>S05/S07</t>
+          <t>podlaha S04 · stěna S03 · strop S06</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>půdorys 1.NP návrh</t>
+          <t>tabulka místností 1.PP stav</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -683,16 +683,16 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>1.04 obývací+kuchyně</t>
+          <t>0.04 sklep 2</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>dům 1.NP návrh</t>
+          <t>dům 1.PP</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>24.4</v>
+        <v>2.3</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -711,12 +711,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>S05/S07</t>
+          <t>podlaha S04 · stěna S03 · strop S06</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>půdorys 1.NP návrh</t>
+          <t>tabulka místností 1.PP stav</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>1.05 ložnice</t>
+          <t>1.01 vstup a chodba</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>14.5</v>
+        <v>9.1</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -756,12 +756,12 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>S05/S07</t>
+          <t>podlaha S05 · stěna S01/S02 · strop S07</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>půdorys 1.NP návrh</t>
+          <t>tabulka místností 1.NP návrh</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -773,16 +773,16 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>2.05 společný pokoj</t>
+          <t>1.02 zádveří</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>dům 2.NP návrh</t>
+          <t>dům 1.NP návrh</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22.1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -801,12 +801,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>S07/S09</t>
+          <t>podlaha S05 · stěna S01/S02 · strop S07</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>půdorys 2.NP návrh</t>
+          <t>tabulka místností 1.NP návrh</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -818,16 +818,16 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2.07 pokoj II</t>
+          <t>1.03 koupelna</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>dům 2.NP návrh</t>
+          <t>dům 1.NP návrh</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>14.4</v>
+        <v>2.6</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -846,12 +846,12 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>S07/S09</t>
+          <t>S05 · obklad stěn · S07</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>půdorys 2.NP návrh</t>
+          <t>tabulka místností 1.NP návrh</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -863,16 +863,16 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>3.05 obývací+kuchyně</t>
+          <t>1.04 obývací místnost + kuchyně</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>dům 3.NP návrh</t>
+          <t>dům 1.NP návrh</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>32.8</v>
+        <v>24.4</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -891,12 +891,12 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>S09/S10</t>
+          <t>podlaha S05 · stěna S01/S02 · strop S07</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>půdorys 3.NP návrh</t>
+          <t>tabulka místností 1.NP návrh</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -908,16 +908,16 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>3.06 ložnice</t>
+          <t>1.05 ložnice</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>dům 3.NP návrh</t>
+          <t>dům 1.NP návrh</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>12.8</v>
+        <v>14.5</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -936,12 +936,12 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>S09/S10</t>
+          <t>podlaha S05 · stěna S01/S02 · strop S07</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>půdorys 3.NP návrh</t>
+          <t>tabulka místností 1.NP návrh</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -953,16 +953,16 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Σ byt 1.NP/2.NP/3.NP</t>
+          <t>1.06 chodba na zahradu</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>dům návrh</t>
+          <t>dům 1.NP návrh</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>150.6</v>
+        <v>3.8</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -981,39 +981,43 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>podlaha S05 · stěna S01/S02 · strop S07</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>48.2+49.6+52.8</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>derived</t>
+          <t>tabulka místností 1.NP návrh</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Fasáda ETICS (S01/S12a)</t>
+          <t>1.08 schodiště do sklepa</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>dům — prvek</t>
+          <t>dům 1.NP návrh</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>276.7</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>38.7</v>
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -1022,39 +1026,43 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>S01 ETICS</t>
+          <t>podlaha S05 · stěna S01/S02 · strop S07</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>38.7×0.55 volná×13.0</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>derived</t>
+          <t>tabulka místností 1.NP návrh</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Sokl (S03)</t>
+          <t>2.01 schodiště</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>dům — prvek</t>
+          <t>dům 2.NP návrh</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>38.7</v>
+        <v>7.3</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -1063,33 +1071,33 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>S03 sanační</t>
+          <t>podlaha S07 · stěna S01/S02 · strop S09</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>38.7×0.6×řadovka0.7</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>estimate</t>
+          <t>tabulka místností 2.NP návrh</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Strop trámový S07</t>
+          <t>2.02 chodba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>dům — prvek</t>
+          <t>dům 2.NP návrh</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>59.5</v>
+        <v>4.2</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
@@ -1108,12 +1116,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>podlaha S07 · stěna S01/S02 · strop S09</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>skladby_per_zone</t>
+          <t>tabulka místností 2.NP návrh</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -1125,16 +1133,16 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Strop ocelobeton S09</t>
+          <t>2.03 koupelna</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>dům — prvek</t>
+          <t>dům 2.NP návrh</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>104.4</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
@@ -1153,12 +1161,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>S09</t>
+          <t>S07 · obklad stěn · S09</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>skladby_per_zone</t>
+          <t>tabulka místností 2.NP návrh</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1170,16 +1178,16 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Střecha S10</t>
+          <t>2.04 chodba</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>dům — prvek</t>
+          <t>dům 2.NP návrh</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>140.94</v>
+        <v>1.6</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
@@ -1198,12 +1206,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>podlaha S07 · stěna S01/S02 · strop S09</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>skladby_per_zone</t>
+          <t>tabulka místností 2.NP návrh</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1215,26 +1223,26 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Krov krokve</t>
+          <t>2.05 společný pokoj</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>dům — prvek</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>dům 2.NP návrh</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>22.1</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
-        <v>156</v>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1243,12 +1251,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>podlaha S07 · stěna S01/S02 · strop S09</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>krov výkres (bm)</t>
+          <t>tabulka místností 2.NP návrh</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -1260,19 +1268,21 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>0.01 sklad zahr. techniky</t>
+          <t>2.06 pokoj I</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>sklad — místnost</t>
+          <t>dům 2.NP návrh</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>2.68</v>
+        <v>9</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -1286,12 +1296,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>S01 podlaha</t>
+          <t>podlaha S07 · stěna S01/S02 · strop S09</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>legenda místností + řez B-B</t>
+          <t>tabulka místností 2.NP návrh</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1303,16 +1313,16 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>1.01 parking stání</t>
+          <t>2.07 pokoj II</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>sklad — střecha</t>
+          <t>dům 2.NP návrh</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>44.6</v>
+        <v>14.4</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
@@ -1331,12 +1341,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>S02 deck</t>
+          <t>podlaha S07 · stěna S01/S02 · strop S09</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>legenda místností (D.1.1.01)</t>
+          <t>tabulka místností 2.NP návrh</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -1348,16 +1358,16 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>1.02 schodiště</t>
+          <t>3.01 schodiště</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>dům 3.NP návrh</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -1376,12 +1386,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>podlaha S09 · stěna S12 · střecha S10</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>legenda (9×179.5×250)</t>
+          <t>tabulka místností 3.NP návrh</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -1393,34 +1403,40 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Opěrná stěna S04 (H-BLOK)</t>
+          <t>3.02 chodba</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>sklad — prvek</t>
+          <t>dům 3.NP návrh</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>11.43</v>
+        <v>4.1</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>S04 prefa 600</t>
+          <t>podlaha S09 · stěna S12 · střecha S10</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>řez A-A: stěna 3000 + zákl. 1000</t>
+          <t>tabulka místností 3.NP návrh</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -1432,22 +1448,26 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Obvodové stěny S03a/b</t>
+          <t>3.03 chodba</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>sklad — prvek</t>
+          <t>dům 3.NP návrh</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="D23" s="4" t="n">
         <v>2.4</v>
       </c>
-      <c r="E23" s="4" t="n">
-        <v>19.4</v>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
@@ -1456,67 +1476,767 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>S03 ztrac. bednění 250</t>
+          <t>podlaha S09 · stěna S12 · střecha S10</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>obvod 19.4 × výška 2.4</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>derived</t>
+          <t>tabulka místností 3.NP návrh</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>3.04 koupelna</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>dům 3.NP návrh</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>S09 · obklad stěn · S10</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>tabulka místností 3.NP návrh</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>3.05 obývací místnost a kuchyně</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>dům 3.NP návrh</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>podlaha S09 · stěna S12 · střecha S10</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>tabulka místností 3.NP návrh</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>3.06 ložnice</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>dům 3.NP návrh</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>podlaha S09 · stěna S12 · střecha S10</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>tabulka místností 3.NP návrh</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Σ podlahy stav 1.PP-3.NP</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>dům stav</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>217.8</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>32.4+59.5+61.0+64.9</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Σ byt 1.NP/2.NP/3.NP</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>dům návrh</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>150.6</v>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>48.2+49.6+52.8</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Fasáda ETICS (S01/S12a)</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>dům — prvek</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>S01 ETICS</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>38.7 × 0.55 volná × 13.0 v</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sokl (S03)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>dům — prvek</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>S03 sanační</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>38.7 × 0.6 × řadovka 0.7 (OVĚŘIT #35)</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Strop trámový S07</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>dům — prvek</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>skladby_per_zone (DXF)</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Strop ocelobeton S09</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>dům — prvek</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>skladby_per_zone (DXF)</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Střecha S10</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>dům — prvek</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>140.94</v>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>skladby_per_zone (DXF)</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Krov krokve (bm)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>dům — prvek</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>krov výkres</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>0.01 sklad zahr. techniky</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>sklad — místnost</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>S01 podlaha</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>legenda místností D.1.1.02 + řez B-B</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>1.01 parking stání</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>sklad — střecha</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>S02 deck (pororošt+IPE180)</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>legenda místností D.1.1.01</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>1.02 schodiště</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>legenda (9×179.5×250)</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Opěrná stěna S04 (H-BLOK 600)</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>sklad — prvek</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>S04 prefa H-BLOK Standard</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>řez A-A: stěna 3000 + zákl. 1000</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>measured</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Obvodové stěny S03a/b</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>sklad — prvek</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>S03 ztrac. bednění 250</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>obvod 19.4 × výška 2.4</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>Stěny pod terénem (HI) S03a+S04</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>sklad — prvek</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C40" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>S03a+S04 HI/drenáž</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>S04 19 + S03a 14 (řez)</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>S03a+S04 HI/protiradon/drenáž</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>S04 19.05 + S03a 14 (řez)</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I24"/>
+  <autoFilter ref="A2:I40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>